--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -1532,10 +1532,10 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1926,10 +1926,10 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
   <si>
     <t>Mat</t>
   </si>
@@ -94,169 +94,154 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MELO</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>JONATHAN ISAI</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
   </si>
   <si>
     <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
   </si>
 </sst>
 </file>
@@ -892,16 +877,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -915,16 +903,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -938,16 +929,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -961,16 +955,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -984,16 +981,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1007,16 +1007,19 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H8">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1092,13 +1095,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
         <v>6.5</v>
@@ -1127,7 +1130,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1144,16 +1147,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1170,16 +1173,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1196,16 +1199,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>69.44</v>
+        <v>75</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1231,7 +1234,7 @@
         <v>89.29000000000001</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1273,16 +1276,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920165</v>
+        <v>23330051920160</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1296,22 +1299,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920302</v>
+        <v>23330051920171</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1319,22 +1322,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920208</v>
+        <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1342,16 +1345,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920323</v>
+        <v>20330051920235</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1365,45 +1368,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920174</v>
+        <v>21330051920323</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920003</v>
+        <v>23330051920174</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1411,16 +1414,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920018</v>
+        <v>21330051920003</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -1434,22 +1437,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920257</v>
+        <v>20330051920018</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1457,16 +1460,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920287</v>
+        <v>21330051920257</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1480,22 +1483,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920353</v>
+        <v>21330051920287</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1503,22 +1506,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920230</v>
+        <v>21330051920347</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1526,16 +1529,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920232</v>
+        <v>21330051920230</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -1552,13 +1555,13 @@
         <v>21330051920235</v>
       </c>
       <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -1572,16 +1575,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920239</v>
+        <v>21330051920249</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -1595,22 +1598,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920249</v>
+        <v>21330051920289</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1618,16 +1621,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920289</v>
+        <v>21330051920337</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -1641,16 +1644,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920337</v>
+        <v>21330051920307</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -1664,16 +1667,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920235</v>
+        <v>19330051920208</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -1687,16 +1690,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920307</v>
+        <v>21330051920316</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -1705,52 +1708,6 @@
         <v>17</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920316</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920319</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="81">
   <si>
     <t>Mat</t>
   </si>
@@ -106,51 +106,57 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>TETLA</t>
   </si>
   <si>
@@ -160,6 +166,12 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -202,46 +214,52 @@
     <t>JOSE RAFAEL</t>
   </si>
   <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1282,10 +1300,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1308,7 +1326,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1328,10 +1346,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1351,10 +1369,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1368,16 +1386,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920323</v>
+        <v>21330051920311</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1391,45 +1409,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920174</v>
+        <v>21330051920328</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920003</v>
+        <v>23330051920174</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1437,16 +1455,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920018</v>
+        <v>21330051920003</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -1460,22 +1478,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920257</v>
+        <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1483,16 +1501,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920287</v>
+        <v>21330051920257</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1506,22 +1524,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920347</v>
+        <v>21330051920287</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1529,22 +1547,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920230</v>
+        <v>21330051920347</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1552,16 +1570,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920235</v>
+        <v>21330051920230</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -1575,16 +1593,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920249</v>
+        <v>21330051920235</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -1598,22 +1616,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920289</v>
+        <v>21330051920249</v>
       </c>
       <c r="B16" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1621,16 +1639,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920337</v>
+        <v>21330051920289</v>
       </c>
       <c r="B17" t="s">
         <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -1644,16 +1662,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920307</v>
+        <v>21330051920337</v>
       </c>
       <c r="B18" t="s">
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -1667,16 +1685,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920208</v>
+        <v>21330051920307</v>
       </c>
       <c r="B19" t="s">
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -1690,16 +1708,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920316</v>
+        <v>19330051920208</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -1708,6 +1726,52 @@
         <v>17</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920316</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920323</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -94,82 +94,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>BAEZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
+    <t>COXCAHUA</t>
   </si>
   <si>
     <t>MARCELINO</t>
@@ -178,49 +109,7 @@
     <t>NAZARIO</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
-    <t>JONATHAN ISAI</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>LUIS EDUARDO</t>
@@ -229,37 +118,7 @@
     <t>EDGAR</t>
   </si>
   <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
+    <t>KARINA</t>
   </si>
 </sst>
 </file>
@@ -1113,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>96.67</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1139,16 +998,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1165,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1191,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -1217,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1262,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1294,484 +1153,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920160</v>
+        <v>21330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920171</v>
+        <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920353</v>
+        <v>21330051920221</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920311</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920328</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920174</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920003</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920018</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920257</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920287</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920347</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920230</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920235</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920249</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920289</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920337</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920307</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920208</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920316</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920323</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -94,28 +94,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
   <si>
     <t>KARINA</t>
@@ -1102,13 +1084,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>7.4</v>
@@ -1121,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1153,70 +1135,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920221</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920018</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920221</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -92,15 +92,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>KARINA</t>
   </si>
 </sst>
 </file>
@@ -1032,16 +1023,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1103,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1133,29 +1124,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -489,7 +489,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -498,7 +498,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -704,7 +710,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -713,7 +719,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -919,7 +931,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -928,7 +940,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -972,7 +972,7 @@
         <v>96.67</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -998,7 +998,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1024,7 +1024,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1050,7 +1050,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1076,7 +1076,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1102,7 +1102,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20231.xlsx
@@ -972,7 +972,7 @@
         <v>96.67</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -998,7 +998,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1024,7 +1024,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1050,7 +1050,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1076,7 +1076,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1102,7 +1102,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
